--- a/rules.xlsx
+++ b/rules.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Desktop\카드 매출 등록 프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3DF409-93DB-4C9F-BA5F-140E05E402B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1AD239-2CB8-4C1B-9909-2DF64522A07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA217618-C2F2-4738-ACD8-AC9D64FF4B01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="39">
   <si>
     <t>BC카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,14 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>판매금액*0.023, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매금액-카드수수료, 소수점 올림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KB카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -72,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>판매금액*0.0228, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>현대카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,22 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>판매금액*0.0152, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매금액*0.0145, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매금액*0.0135, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매금액*0.015, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하나카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>판매금액*0.0151, 소수점 버림 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>삼성카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,61 +99,84 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>카드사명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
-    <t>하나체크</t>
-  </si>
-  <si>
-    <t>신한체크</t>
-  </si>
-  <si>
-    <t>우리체크</t>
-  </si>
-  <si>
-    <t>농협체크</t>
-  </si>
-  <si>
-    <t>기업(IBK)체크</t>
-  </si>
-  <si>
-    <t>부산체크</t>
-  </si>
-  <si>
-    <t>카카오체크</t>
+    <t>삼성</t>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계*0.023, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.0228, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.0152, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.0145, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.0135, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.015, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계*0.0151, 소수점 버림 처리</t>
+  </si>
+  <si>
+    <t>합계-카드수수료, 소수점 올림 처리</t>
+  </si>
+  <si>
+    <t>키워드1(카드사명)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키워드2(유형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>체크</t>
-  </si>
-  <si>
-    <t>삼성</t>
-  </si>
-  <si>
-    <t>BC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>신한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>현대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>롯데</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국민(KB)체크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB(국민)</t>
+  </si>
+  <si>
+    <t>우리</t>
+  </si>
+  <si>
+    <t>농협</t>
+  </si>
+  <si>
+    <t>부산</t>
+  </si>
+  <si>
+    <t>카카오</t>
+  </si>
+  <si>
+    <t>국민, KB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기업, IBK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,119 +559,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFB0C65-6DDE-4E7C-8AC9-6BD8FEF40849}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
-    <col min="3" max="3" width="50.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,237 +698,268 @@
         <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{3FFB0C65-6DDE-4E7C-8AC9-6BD8FEF40849}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F20">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\win10\Desktop\카드 매출 등록 프로그램\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1AD239-2CB8-4C1B-9909-2DF64522A07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8CA50B-B044-4F57-9285-DBC5728D18A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA217618-C2F2-4738-ACD8-AC9D64FF4B01}"/>
+    <workbookView xWindow="28500" yWindow="0" windowWidth="20865" windowHeight="15480" xr2:uid="{BA217618-C2F2-4738-ACD8-AC9D64FF4B01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,30 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>합계*0.023, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.0228, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.0152, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.0145, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.0135, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.015, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계*0.0151, 소수점 버림 처리</t>
-  </si>
-  <si>
-    <t>합계-카드수수료, 소수점 올림 처리</t>
-  </si>
-  <si>
     <t>키워드1(카드사명)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,6 +154,30 @@
   <si>
     <t>기업, IBK</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계*0.0152</t>
+  </si>
+  <si>
+    <t>합계*0.0145</t>
+  </si>
+  <si>
+    <t>합계*0.0135</t>
+  </si>
+  <si>
+    <t>합계*0.023</t>
+  </si>
+  <si>
+    <t>합계*0.015</t>
+  </si>
+  <si>
+    <t>합계*0.0228</t>
+  </si>
+  <si>
+    <t>합계*0.0151</t>
+  </si>
+  <si>
+    <t>합계-카드수수료</t>
   </si>
 </sst>
 </file>
@@ -575,10 +575,10 @@
         <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
@@ -595,19 +595,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -618,16 +618,16 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -635,19 +635,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -655,19 +655,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -675,19 +675,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -695,19 +695,19 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -715,19 +715,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -735,19 +735,19 @@
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -756,16 +756,16 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -780,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,19 +791,19 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -811,17 +811,17 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -836,10 +836,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -854,10 +854,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -865,19 +865,19 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -892,10 +892,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -906,16 +906,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -930,10 +930,10 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -948,10 +948,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
